--- a/docs/mci_cog_igm_rules_dcc.xlsx
+++ b/docs/mci_cog_igm_rules_dcc.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bullenca/Work/CCDIDC/CCDIDC-1950/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bullenca/Work/Repos/ChildhoodCancerDataInitiative-Prefect_Pipeline/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176B4ED1-C734-C24F-9A84-1C3AF7176F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67695254-1F30-9848-A275-937909D91686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17820" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
+    <workbookView xWindow="20320" yWindow="-19520" windowWidth="30240" windowHeight="17820" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
   </bookViews>
   <sheets>
     <sheet name="cog_rules" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="223">
   <si>
     <t>source</t>
   </si>
@@ -2157,8 +2157,8 @@
       <c r="I24" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J24">
-        <v>-999</v>
+      <c r="J24" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -2508,8 +2508,8 @@
       <c r="I39" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J39">
-        <v>-999</v>
+      <c r="J39" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -2850,8 +2850,8 @@
       <c r="I54" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J54">
-        <v>-999</v>
+      <c r="J54" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
@@ -3201,8 +3201,8 @@
       <c r="I69" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J69">
-        <v>-999</v>
+      <c r="J69" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
@@ -3549,8 +3549,8 @@
       <c r="I84" t="s">
         <v>85</v>
       </c>
-      <c r="J84">
-        <v>-999</v>
+      <c r="J84" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
@@ -3796,6 +3796,9 @@
       <c r="F95" t="s">
         <v>74</v>
       </c>
+      <c r="G95" t="s">
+        <v>47</v>
+      </c>
       <c r="H95" t="s">
         <v>73</v>
       </c>
@@ -3897,8 +3900,8 @@
       <c r="I99" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J99">
-        <v>-999</v>
+      <c r="J99" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
@@ -4254,8 +4257,8 @@
       <c r="I114" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J114">
-        <v>-999</v>
+      <c r="J114" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
@@ -4605,8 +4608,8 @@
       <c r="I129" t="s">
         <v>85</v>
       </c>
-      <c r="J129">
-        <v>-999</v>
+      <c r="J129" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
@@ -4962,8 +4965,8 @@
       <c r="I144" t="s">
         <v>85</v>
       </c>
-      <c r="J144">
-        <v>-999</v>
+      <c r="J144" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
@@ -5316,8 +5319,8 @@
       <c r="I159" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J159">
-        <v>-999</v>
+      <c r="J159" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.2">

--- a/docs/mci_cog_igm_rules_dcc.xlsx
+++ b/docs/mci_cog_igm_rules_dcc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bullenca/Work/Repos/ChildhoodCancerDataInitiative-Prefect_Pipeline/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67695254-1F30-9848-A275-937909D91686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587CDC4F-336B-044A-9F8F-F60D55122B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20320" yWindow="-19520" windowWidth="30240" windowHeight="17820" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19840" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
   </bookViews>
   <sheets>
     <sheet name="cog_rules" sheetId="1" r:id="rId1"/>
@@ -1588,6 +1588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K300"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1635,7 +1636,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1658,7 +1659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1678,7 +1679,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1701,7 +1702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1724,7 +1725,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1747,7 +1748,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1770,7 +1771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1790,7 +1791,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1819,7 +1820,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1842,7 +1843,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1865,7 +1866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1888,7 +1889,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1914,7 +1915,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1937,7 +1938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1957,7 +1958,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1977,7 +1978,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1997,7 +1998,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2020,7 +2021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -2040,7 +2041,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2060,7 +2061,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2083,7 +2084,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -2106,7 +2107,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -2129,7 +2130,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -2161,7 +2162,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -2184,7 +2185,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -2207,7 +2208,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -2236,7 +2237,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -2259,7 +2260,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2279,7 +2280,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -2305,7 +2306,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -2325,7 +2326,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -2351,7 +2352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -2371,7 +2372,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -2414,7 +2415,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -2437,7 +2438,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -2460,7 +2461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -2480,7 +2481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -2512,7 +2513,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -2532,7 +2533,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -2555,7 +2556,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -2581,7 +2582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -2604,7 +2605,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -2624,7 +2625,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -2644,7 +2645,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>10</v>
       </c>
@@ -2664,7 +2665,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>10</v>
       </c>
@@ -2687,7 +2688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2730,7 +2731,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -2756,7 +2757,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>10</v>
       </c>
@@ -2779,7 +2780,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>10</v>
       </c>
@@ -2802,7 +2803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -2825,7 +2826,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -2854,7 +2855,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -2877,7 +2878,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -2900,7 +2901,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -2926,7 +2927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -2946,7 +2947,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -2966,7 +2967,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -2989,7 +2990,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -3012,7 +3013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -3035,7 +3036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -3058,7 +3059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -3081,7 +3082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -3107,7 +3108,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -3130,7 +3131,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -3153,7 +3154,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>10</v>
       </c>
@@ -3176,7 +3177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>10</v>
       </c>
@@ -3205,7 +3206,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -3225,7 +3226,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -3248,7 +3249,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>10</v>
       </c>
@@ -3274,7 +3275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>10</v>
       </c>
@@ -3294,7 +3295,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>10</v>
       </c>
@@ -3314,7 +3315,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>10</v>
       </c>
@@ -3337,7 +3338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>10</v>
       </c>
@@ -3360,7 +3361,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>10</v>
       </c>
@@ -3383,7 +3384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -3406,7 +3407,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>10</v>
       </c>
@@ -3429,7 +3430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -3455,7 +3456,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>10</v>
       </c>
@@ -3478,7 +3479,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -3501,7 +3502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -3524,7 +3525,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>10</v>
       </c>
@@ -3553,7 +3554,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -3576,7 +3577,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>10</v>
       </c>
@@ -3599,7 +3600,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -3625,7 +3626,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>10</v>
       </c>
@@ -3645,7 +3646,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>10</v>
       </c>
@@ -3665,7 +3666,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -3688,7 +3689,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>10</v>
       </c>
@@ -3711,7 +3712,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>10</v>
       </c>
@@ -3734,7 +3735,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>10</v>
       </c>
@@ -3757,7 +3758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>10</v>
       </c>
@@ -3780,7 +3781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>10</v>
       </c>
@@ -3806,7 +3807,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>10</v>
       </c>
@@ -3829,7 +3830,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>10</v>
       </c>
@@ -3852,7 +3853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>10</v>
       </c>
@@ -3875,7 +3876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>10</v>
       </c>
@@ -3904,7 +3905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -3924,7 +3925,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>10</v>
       </c>
@@ -3947,7 +3948,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -3973,7 +3974,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>10</v>
       </c>
@@ -3996,7 +3997,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -4019,7 +4020,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>10</v>
       </c>
@@ -4045,7 +4046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -4065,7 +4066,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>10</v>
       </c>
@@ -4091,7 +4092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>10</v>
       </c>
@@ -4114,7 +4115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>10</v>
       </c>
@@ -4137,7 +4138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>10</v>
       </c>
@@ -4163,7 +4164,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>10</v>
       </c>
@@ -4186,7 +4187,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>10</v>
       </c>
@@ -4209,7 +4210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>10</v>
       </c>
@@ -4232,7 +4233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -4261,7 +4262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -4284,7 +4285,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -4307,7 +4308,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>10</v>
       </c>
@@ -4333,7 +4334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>10</v>
       </c>
@@ -4356,7 +4357,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>10</v>
       </c>
@@ -4379,7 +4380,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>10</v>
       </c>
@@ -4402,7 +4403,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>10</v>
       </c>
@@ -4425,7 +4426,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>10</v>
       </c>
@@ -4451,7 +4452,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>10</v>
       </c>
@@ -4471,7 +4472,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>10</v>
       </c>
@@ -4488,7 +4489,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>10</v>
       </c>
@@ -4514,7 +4515,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>10</v>
       </c>
@@ -4537,7 +4538,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>10</v>
       </c>
@@ -4560,7 +4561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -4583,7 +4584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -4612,7 +4613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -4632,7 +4633,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -4655,7 +4656,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>10</v>
       </c>
@@ -4681,7 +4682,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>10</v>
       </c>
@@ -4704,7 +4705,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -4727,7 +4728,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>10</v>
       </c>
@@ -4750,7 +4751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>10</v>
       </c>
@@ -4773,7 +4774,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>10</v>
       </c>
@@ -4799,7 +4800,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>10</v>
       </c>
@@ -4819,7 +4820,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>10</v>
       </c>
@@ -4842,7 +4843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>10</v>
       </c>
@@ -4868,7 +4869,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -4891,7 +4892,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -4914,7 +4915,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -4937,7 +4938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -4969,7 +4970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -4992,7 +4993,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -5015,7 +5016,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -5041,7 +5042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>10</v>
       </c>
@@ -5064,7 +5065,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -5084,7 +5085,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -5107,7 +5108,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>10</v>
       </c>
@@ -5130,7 +5131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>10</v>
       </c>
@@ -5156,7 +5157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>10</v>
       </c>
@@ -5176,7 +5177,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>10</v>
       </c>
@@ -5199,7 +5200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>10</v>
       </c>
@@ -5225,7 +5226,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>10</v>
       </c>
@@ -5248,7 +5249,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>10</v>
       </c>
@@ -5271,7 +5272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>10</v>
       </c>
@@ -5294,7 +5295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>10</v>
       </c>
@@ -5323,7 +5324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>10</v>
       </c>
@@ -5343,7 +5344,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>10</v>
       </c>
@@ -5366,7 +5367,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>10</v>
       </c>
@@ -5392,7 +5393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>10</v>
       </c>
@@ -5412,7 +5413,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>10</v>
       </c>
@@ -5432,7 +5433,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>10</v>
       </c>
@@ -5455,7 +5456,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>10</v>
       </c>
@@ -5478,7 +5479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>10</v>
       </c>
@@ -5501,7 +5502,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>10</v>
       </c>
@@ -5524,7 +5525,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>10</v>
       </c>
@@ -5547,7 +5548,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>10</v>
       </c>
@@ -5573,7 +5574,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>10</v>
       </c>
@@ -5596,7 +5597,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>10</v>
       </c>
@@ -5619,7 +5620,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>10</v>
       </c>
@@ -5639,7 +5640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>10</v>
       </c>
@@ -5665,7 +5666,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>10</v>
       </c>
@@ -5688,7 +5689,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>10</v>
       </c>
@@ -5708,7 +5709,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>10</v>
       </c>
@@ -5731,7 +5732,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>10</v>
       </c>
@@ -5751,7 +5752,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>10</v>
       </c>
@@ -5771,7 +5772,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>10</v>
       </c>
@@ -5791,7 +5792,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>10</v>
       </c>
@@ -5811,7 +5812,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>10</v>
       </c>
@@ -5831,7 +5832,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>10</v>
       </c>
@@ -5851,7 +5852,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>10</v>
       </c>
@@ -5871,7 +5872,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>10</v>
       </c>
@@ -5891,7 +5892,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>10</v>
       </c>
@@ -5911,7 +5912,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>10</v>
       </c>
@@ -5934,7 +5935,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>10</v>
       </c>
@@ -5954,7 +5955,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>10</v>
       </c>
@@ -5986,7 +5987,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>10</v>
       </c>
@@ -6006,7 +6007,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>10</v>
       </c>
@@ -6029,7 +6030,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>10</v>
       </c>
@@ -6052,7 +6053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>10</v>
       </c>
@@ -6075,7 +6076,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>10</v>
       </c>
@@ -6098,7 +6099,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>10</v>
       </c>
@@ -6118,7 +6119,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>10</v>
       </c>
@@ -6144,7 +6145,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>10</v>
       </c>
@@ -6167,7 +6168,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -6196,7 +6197,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>10</v>
       </c>
@@ -6219,7 +6220,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>10</v>
       </c>
@@ -6245,7 +6246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>10</v>
       </c>
@@ -6265,7 +6266,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>10</v>
       </c>
@@ -6285,7 +6286,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>10</v>
       </c>
@@ -6305,7 +6306,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>10</v>
       </c>
@@ -6328,7 +6329,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>10</v>
       </c>
@@ -6348,7 +6349,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -6371,7 +6372,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>10</v>
       </c>
@@ -6391,7 +6392,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>10</v>
       </c>
@@ -6411,7 +6412,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>10</v>
       </c>
@@ -6431,7 +6432,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -6454,7 +6455,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -6474,7 +6475,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>10</v>
       </c>
@@ -6500,7 +6501,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -6523,7 +6524,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>10</v>
       </c>
@@ -6546,7 +6547,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>10</v>
       </c>
@@ -6569,7 +6570,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>10</v>
       </c>
@@ -6709,9 +6710,6 @@
       <c r="G221" t="s">
         <v>221</v>
       </c>
-      <c r="J221">
-        <v>-999</v>
-      </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
@@ -6755,6 +6753,9 @@
       <c r="G223" t="s">
         <v>191</v>
       </c>
+      <c r="J223">
+        <v>-999</v>
+      </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
@@ -6802,7 +6803,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>10</v>
       </c>
@@ -6825,7 +6826,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>10</v>
       </c>
@@ -6845,7 +6846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>10</v>
       </c>
@@ -6871,7 +6872,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>10</v>
       </c>
@@ -6894,7 +6895,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>10</v>
       </c>
@@ -6917,7 +6918,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>10</v>
       </c>
@@ -6940,7 +6941,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>10</v>
       </c>
@@ -6963,7 +6964,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>10</v>
       </c>
@@ -6992,7 +6993,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>10</v>
       </c>
@@ -7012,7 +7013,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>10</v>
       </c>
@@ -7032,7 +7033,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>10</v>
       </c>
@@ -7052,7 +7053,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>10</v>
       </c>
@@ -7072,7 +7073,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>10</v>
       </c>
@@ -7092,7 +7093,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>10</v>
       </c>
@@ -7112,7 +7113,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>10</v>
       </c>
@@ -7132,7 +7133,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>10</v>
       </c>
@@ -7155,7 +7156,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>10</v>
       </c>
@@ -7175,7 +7176,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>10</v>
       </c>
@@ -7201,7 +7202,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>10</v>
       </c>
@@ -7224,7 +7225,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>10</v>
       </c>
@@ -7247,7 +7248,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>10</v>
       </c>
@@ -7270,7 +7271,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>10</v>
       </c>
@@ -7293,7 +7294,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>10</v>
       </c>
@@ -7322,7 +7323,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -7342,7 +7343,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>10</v>
       </c>
@@ -7362,7 +7363,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>10</v>
       </c>
@@ -7382,7 +7383,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>10</v>
       </c>
@@ -7402,7 +7403,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>10</v>
       </c>
@@ -7422,7 +7423,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>10</v>
       </c>
@@ -7442,7 +7443,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>10</v>
       </c>
@@ -7462,7 +7463,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>10</v>
       </c>
@@ -7485,7 +7486,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>10</v>
       </c>
@@ -7505,7 +7506,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>10</v>
       </c>
@@ -7531,7 +7532,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>10</v>
       </c>
@@ -7554,7 +7555,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>10</v>
       </c>
@@ -7577,7 +7578,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>10</v>
       </c>
@@ -7600,7 +7601,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>10</v>
       </c>
@@ -7623,7 +7624,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>10</v>
       </c>
@@ -7652,7 +7653,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>10</v>
       </c>
@@ -7672,7 +7673,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>10</v>
       </c>
@@ -7692,7 +7693,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>10</v>
       </c>
@@ -7712,7 +7713,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>10</v>
       </c>
@@ -7732,7 +7733,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>10</v>
       </c>
@@ -7752,7 +7753,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>10</v>
       </c>
@@ -7772,7 +7773,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>10</v>
       </c>
@@ -7792,7 +7793,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>10</v>
       </c>
@@ -7815,7 +7816,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>10</v>
       </c>
@@ -7835,7 +7836,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>10</v>
       </c>
@@ -7861,7 +7862,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>10</v>
       </c>
@@ -7884,7 +7885,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>10</v>
       </c>
@@ -7907,7 +7908,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>10</v>
       </c>
@@ -7930,7 +7931,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>10</v>
       </c>
@@ -7953,7 +7954,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>10</v>
       </c>
@@ -7982,7 +7983,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>10</v>
       </c>
@@ -8002,7 +8003,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>10</v>
       </c>
@@ -8022,7 +8023,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>10</v>
       </c>
@@ -8042,7 +8043,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>10</v>
       </c>
@@ -8062,7 +8063,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>10</v>
       </c>
@@ -8082,7 +8083,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>10</v>
       </c>
@@ -8102,7 +8103,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>10</v>
       </c>
@@ -8122,7 +8123,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>10</v>
       </c>
@@ -8145,7 +8146,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>10</v>
       </c>
@@ -8165,7 +8166,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>10</v>
       </c>
@@ -8187,7 +8188,7 @@
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>10</v>
       </c>
@@ -8210,7 +8211,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>10</v>
       </c>
@@ -8230,7 +8231,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>10</v>
       </c>
@@ -8253,7 +8254,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>10</v>
       </c>
@@ -8276,7 +8277,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>10</v>
       </c>
@@ -8305,7 +8306,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>10</v>
       </c>
@@ -8325,7 +8326,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>10</v>
       </c>
@@ -8345,7 +8346,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>10</v>
       </c>
@@ -8365,7 +8366,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>10</v>
       </c>
@@ -8385,7 +8386,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>10</v>
       </c>
@@ -8405,7 +8406,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>10</v>
       </c>
@@ -8425,7 +8426,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>10</v>
       </c>
@@ -8446,7 +8447,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K300" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}"/>
+  <autoFilter ref="A1:K300" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="treatment_surgery"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/docs/mci_cog_igm_rules_dcc.xlsx
+++ b/docs/mci_cog_igm_rules_dcc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bullenca/Work/Repos/ChildhoodCancerDataInitiative-Prefect_Pipeline/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587CDC4F-336B-044A-9F8F-F60D55122B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA4E67F-788D-A542-9D06-943559000E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19840" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
+    <workbookView xWindow="4080" yWindow="1600" windowWidth="30240" windowHeight="18980" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
   </bookViews>
   <sheets>
     <sheet name="cog_rules" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="222">
   <si>
     <t>source</t>
   </si>
@@ -622,9 +622,6 @@
   </si>
   <si>
     <t>\s\([A-Za-z, ]+\)</t>
-  </si>
-  <si>
-    <t>\s\([A-Za-z0-9, \-\.]+\)?</t>
   </si>
   <si>
     <t>treatment_chemotherapy_immunotherapy</t>
@@ -1588,7 +1585,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K300"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1636,7 +1632,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1647,7 +1643,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F2" t="s">
         <v>26</v>
@@ -1659,7 +1655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1679,7 +1675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1702,7 +1698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1725,7 +1721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1736,19 +1732,19 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
         <v>218</v>
       </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1759,7 +1755,7 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
@@ -1771,7 +1767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1791,7 +1787,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1820,7 +1816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1843,7 +1839,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1866,7 +1862,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1889,7 +1885,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1915,7 +1911,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1938,7 +1934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1958,7 +1954,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1978,7 +1974,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1998,7 +1994,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2021,7 +2017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -2041,7 +2037,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2061,7 +2057,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2084,7 +2080,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -2095,7 +2091,7 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
@@ -2107,7 +2103,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -2130,7 +2126,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -2162,7 +2158,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -2185,7 +2181,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -2208,7 +2204,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -2237,7 +2233,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -2260,7 +2256,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2280,7 +2276,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -2306,7 +2302,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -2326,7 +2322,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -2352,7 +2348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -2372,7 +2368,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -2389,7 +2385,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -2415,7 +2411,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -2438,7 +2434,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -2449,7 +2445,7 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
@@ -2461,7 +2457,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -2481,7 +2477,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -2513,7 +2509,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -2533,7 +2529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -2556,7 +2552,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -2582,7 +2578,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -2605,7 +2601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -2625,7 +2621,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -2645,7 +2641,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>10</v>
       </c>
@@ -2665,7 +2661,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>10</v>
       </c>
@@ -2688,7 +2684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>10</v>
       </c>
@@ -2708,7 +2704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2731,7 +2727,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -2757,7 +2753,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>10</v>
       </c>
@@ -2780,7 +2776,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>10</v>
       </c>
@@ -2791,7 +2787,7 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
@@ -2803,7 +2799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>10</v>
       </c>
@@ -2826,7 +2822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -2855,7 +2851,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>10</v>
       </c>
@@ -2878,7 +2874,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -2901,7 +2897,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -2927,7 +2923,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -2947,7 +2943,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -2967,7 +2963,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -2990,7 +2986,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -3013,7 +3009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -3036,7 +3032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -3059,7 +3055,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -3082,7 +3078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>10</v>
       </c>
@@ -3108,7 +3104,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>10</v>
       </c>
@@ -3131,7 +3127,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -3142,7 +3138,7 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
@@ -3154,7 +3150,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>10</v>
       </c>
@@ -3177,7 +3173,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>10</v>
       </c>
@@ -3206,7 +3202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>10</v>
       </c>
@@ -3226,7 +3222,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -3249,7 +3245,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>10</v>
       </c>
@@ -3275,7 +3271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>10</v>
       </c>
@@ -3295,7 +3291,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>10</v>
       </c>
@@ -3315,7 +3311,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>10</v>
       </c>
@@ -3338,7 +3334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>10</v>
       </c>
@@ -3361,7 +3357,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>10</v>
       </c>
@@ -3384,7 +3380,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -3407,7 +3403,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>10</v>
       </c>
@@ -3430,7 +3426,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -3456,7 +3452,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>10</v>
       </c>
@@ -3479,7 +3475,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -3490,7 +3486,7 @@
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
@@ -3502,7 +3498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>10</v>
       </c>
@@ -3525,7 +3521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>10</v>
       </c>
@@ -3554,7 +3550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -3577,7 +3573,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>10</v>
       </c>
@@ -3600,7 +3596,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>10</v>
       </c>
@@ -3626,7 +3622,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>10</v>
       </c>
@@ -3646,7 +3642,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>10</v>
       </c>
@@ -3666,7 +3662,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>10</v>
       </c>
@@ -3689,7 +3685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>10</v>
       </c>
@@ -3712,7 +3708,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>10</v>
       </c>
@@ -3735,7 +3731,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>10</v>
       </c>
@@ -3758,7 +3754,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>10</v>
       </c>
@@ -3781,7 +3777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>10</v>
       </c>
@@ -3807,7 +3803,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>10</v>
       </c>
@@ -3830,7 +3826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>10</v>
       </c>
@@ -3841,7 +3837,7 @@
         <v>20</v>
       </c>
       <c r="E97" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F97" t="s">
         <v>26</v>
@@ -3853,7 +3849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>10</v>
       </c>
@@ -3876,7 +3872,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>10</v>
       </c>
@@ -3905,7 +3901,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -3925,7 +3921,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>10</v>
       </c>
@@ -3948,7 +3944,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -3974,7 +3970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>10</v>
       </c>
@@ -3997,7 +3993,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -4020,7 +4016,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>10</v>
       </c>
@@ -4046,7 +4042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>10</v>
       </c>
@@ -4066,7 +4062,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>10</v>
       </c>
@@ -4092,7 +4088,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>10</v>
       </c>
@@ -4115,7 +4111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>10</v>
       </c>
@@ -4138,7 +4134,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>10</v>
       </c>
@@ -4164,7 +4160,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>10</v>
       </c>
@@ -4187,7 +4183,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>10</v>
       </c>
@@ -4198,7 +4194,7 @@
         <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F112" t="s">
         <v>26</v>
@@ -4210,7 +4206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>10</v>
       </c>
@@ -4233,7 +4229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -4262,7 +4258,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>10</v>
       </c>
@@ -4285,7 +4281,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>10</v>
       </c>
@@ -4308,7 +4304,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>10</v>
       </c>
@@ -4334,7 +4330,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>10</v>
       </c>
@@ -4357,7 +4353,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>10</v>
       </c>
@@ -4380,7 +4376,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>10</v>
       </c>
@@ -4403,7 +4399,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>10</v>
       </c>
@@ -4426,7 +4422,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>10</v>
       </c>
@@ -4452,7 +4448,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>10</v>
       </c>
@@ -4472,7 +4468,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>10</v>
       </c>
@@ -4489,7 +4485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>10</v>
       </c>
@@ -4515,7 +4511,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>10</v>
       </c>
@@ -4538,7 +4534,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>10</v>
       </c>
@@ -4549,7 +4545,7 @@
         <v>20</v>
       </c>
       <c r="E127" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F127" t="s">
         <v>26</v>
@@ -4561,7 +4557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -4584,7 +4580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -4613,7 +4609,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -4633,7 +4629,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -4656,7 +4652,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>10</v>
       </c>
@@ -4682,7 +4678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>10</v>
       </c>
@@ -4705,7 +4701,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>10</v>
       </c>
@@ -4728,7 +4724,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>10</v>
       </c>
@@ -4751,7 +4747,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>10</v>
       </c>
@@ -4774,7 +4770,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>10</v>
       </c>
@@ -4800,7 +4796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>10</v>
       </c>
@@ -4820,7 +4816,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>10</v>
       </c>
@@ -4843,7 +4839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>10</v>
       </c>
@@ -4869,7 +4865,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>10</v>
       </c>
@@ -4892,7 +4888,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -4903,7 +4899,7 @@
         <v>20</v>
       </c>
       <c r="E142" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F142" t="s">
         <v>26</v>
@@ -4915,7 +4911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>10</v>
       </c>
@@ -4938,7 +4934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>10</v>
       </c>
@@ -4970,7 +4966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>10</v>
       </c>
@@ -4993,7 +4989,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>10</v>
       </c>
@@ -5016,7 +5012,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>10</v>
       </c>
@@ -5042,7 +5038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>10</v>
       </c>
@@ -5065,7 +5061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>10</v>
       </c>
@@ -5085,7 +5081,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>10</v>
       </c>
@@ -5108,7 +5104,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>10</v>
       </c>
@@ -5131,7 +5127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>10</v>
       </c>
@@ -5157,7 +5153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>10</v>
       </c>
@@ -5177,7 +5173,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>10</v>
       </c>
@@ -5200,7 +5196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>10</v>
       </c>
@@ -5226,7 +5222,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>10</v>
       </c>
@@ -5249,7 +5245,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>10</v>
       </c>
@@ -5260,7 +5256,7 @@
         <v>20</v>
       </c>
       <c r="E157" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F157" t="s">
         <v>26</v>
@@ -5272,7 +5268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>10</v>
       </c>
@@ -5295,7 +5291,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>10</v>
       </c>
@@ -5324,7 +5320,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>10</v>
       </c>
@@ -5344,7 +5340,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>10</v>
       </c>
@@ -5367,7 +5363,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>10</v>
       </c>
@@ -5393,7 +5389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>10</v>
       </c>
@@ -5413,7 +5409,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>10</v>
       </c>
@@ -5433,7 +5429,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>10</v>
       </c>
@@ -5456,7 +5452,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>10</v>
       </c>
@@ -5479,7 +5475,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>10</v>
       </c>
@@ -5502,7 +5498,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>10</v>
       </c>
@@ -5525,7 +5521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>10</v>
       </c>
@@ -5548,7 +5544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>10</v>
       </c>
@@ -5574,7 +5570,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>10</v>
       </c>
@@ -5597,7 +5593,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>10</v>
       </c>
@@ -5608,7 +5604,7 @@
         <v>144</v>
       </c>
       <c r="E172" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F172" t="s">
         <v>26</v>
@@ -5620,7 +5616,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>10</v>
       </c>
@@ -5640,7 +5636,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>10</v>
       </c>
@@ -5666,7 +5662,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>10</v>
       </c>
@@ -5689,7 +5685,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>10</v>
       </c>
@@ -5709,7 +5705,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>10</v>
       </c>
@@ -5732,7 +5728,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>10</v>
       </c>
@@ -5752,7 +5748,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>10</v>
       </c>
@@ -5772,7 +5768,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>10</v>
       </c>
@@ -5792,7 +5788,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>10</v>
       </c>
@@ -5812,7 +5808,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>10</v>
       </c>
@@ -5832,7 +5828,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>10</v>
       </c>
@@ -5852,7 +5848,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>10</v>
       </c>
@@ -5872,7 +5868,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>10</v>
       </c>
@@ -5892,7 +5888,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>10</v>
       </c>
@@ -5912,7 +5908,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>10</v>
       </c>
@@ -5923,7 +5919,7 @@
         <v>130</v>
       </c>
       <c r="E187" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F187" t="s">
         <v>26</v>
@@ -5935,7 +5931,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>10</v>
       </c>
@@ -5955,7 +5951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>10</v>
       </c>
@@ -5987,7 +5983,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>10</v>
       </c>
@@ -6007,7 +6003,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>10</v>
       </c>
@@ -6030,7 +6026,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>10</v>
       </c>
@@ -6053,7 +6049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>10</v>
       </c>
@@ -6076,7 +6072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>10</v>
       </c>
@@ -6087,7 +6083,7 @@
         <v>117</v>
       </c>
       <c r="E194" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F194" t="s">
         <v>26</v>
@@ -6099,7 +6095,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>10</v>
       </c>
@@ -6119,7 +6115,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>10</v>
       </c>
@@ -6145,7 +6141,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>10</v>
       </c>
@@ -6168,7 +6164,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -6188,7 +6184,7 @@
         <v>36</v>
       </c>
       <c r="G198" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H198" t="s">
         <v>177</v>
@@ -6197,7 +6193,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>10</v>
       </c>
@@ -6220,7 +6216,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>10</v>
       </c>
@@ -6246,7 +6242,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>10</v>
       </c>
@@ -6266,7 +6262,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>10</v>
       </c>
@@ -6286,7 +6282,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>10</v>
       </c>
@@ -6306,7 +6302,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>10</v>
       </c>
@@ -6329,7 +6325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>10</v>
       </c>
@@ -6349,7 +6345,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -6372,7 +6368,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>10</v>
       </c>
@@ -6392,7 +6388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>10</v>
       </c>
@@ -6412,7 +6408,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>10</v>
       </c>
@@ -6432,7 +6428,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -6443,7 +6439,7 @@
         <v>118</v>
       </c>
       <c r="E210" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F210" t="s">
         <v>26</v>
@@ -6455,7 +6451,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -6475,7 +6471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>10</v>
       </c>
@@ -6501,7 +6497,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -6524,7 +6520,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>10</v>
       </c>
@@ -6547,7 +6543,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>10</v>
       </c>
@@ -6570,7 +6566,7 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>10</v>
       </c>
@@ -6604,7 +6600,7 @@
         <v>124</v>
       </c>
       <c r="E217" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F217" t="s">
         <v>26</v>
@@ -6708,7 +6704,7 @@
         <v>122</v>
       </c>
       <c r="G221" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.2">
@@ -6797,24 +6793,24 @@
         <v>123</v>
       </c>
       <c r="G225" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I225" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>10</v>
       </c>
       <c r="B226" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D226" t="s">
         <v>106</v>
       </c>
       <c r="E226" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F226" t="s">
         <v>26</v>
@@ -6826,12 +6822,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>10</v>
       </c>
       <c r="B227" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D227" t="s">
         <v>106</v>
@@ -6846,12 +6842,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>10</v>
       </c>
       <c r="B228" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D228" t="s">
         <v>106</v>
@@ -6869,15 +6865,15 @@
         <v>73</v>
       </c>
       <c r="I228" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>10</v>
       </c>
       <c r="B229" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D229" t="s">
         <v>106</v>
@@ -6895,18 +6891,18 @@
         <v>193</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>10</v>
       </c>
       <c r="B230" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D230" t="s">
         <v>106</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F230" t="s">
         <v>26</v>
@@ -6915,15 +6911,15 @@
         <v>26</v>
       </c>
       <c r="I230" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>10</v>
       </c>
       <c r="B231" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D231" t="s">
         <v>106</v>
@@ -6941,12 +6937,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>10</v>
       </c>
       <c r="B232" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D232" t="s">
         <v>106</v>
@@ -6964,12 +6960,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>10</v>
       </c>
       <c r="B233" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C233" t="b">
         <v>1</v>
@@ -6984,21 +6980,15 @@
         <v>36</v>
       </c>
       <c r="G233" t="s">
-        <v>198</v>
-      </c>
-      <c r="H233" t="s">
-        <v>177</v>
-      </c>
-      <c r="I233" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>10</v>
+      </c>
+      <c r="B234" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A234" t="s">
-        <v>10</v>
-      </c>
-      <c r="B234" t="s">
-        <v>196</v>
       </c>
       <c r="D234" t="s">
         <v>106</v>
@@ -7013,12 +7003,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>10</v>
       </c>
       <c r="B235" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D235" t="s">
         <v>106</v>
@@ -7033,12 +7023,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>10</v>
       </c>
       <c r="B236" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D236" t="s">
         <v>106</v>
@@ -7053,12 +7043,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>10</v>
       </c>
       <c r="B237" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D237" t="s">
         <v>106</v>
@@ -7073,12 +7063,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>10</v>
       </c>
       <c r="B238" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D238" t="s">
         <v>106</v>
@@ -7093,12 +7083,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>10</v>
       </c>
       <c r="B239" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D239" t="s">
         <v>106</v>
@@ -7113,12 +7103,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>10</v>
       </c>
       <c r="B240" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D240" t="s">
         <v>106</v>
@@ -7133,18 +7123,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>10</v>
       </c>
       <c r="B241" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D241" t="s">
         <v>106</v>
       </c>
       <c r="E241" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F241" t="s">
         <v>26</v>
@@ -7156,12 +7146,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>10</v>
       </c>
       <c r="B242" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D242" t="s">
         <v>106</v>
@@ -7176,12 +7166,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>10</v>
       </c>
       <c r="B243" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D243" t="s">
         <v>106</v>
@@ -7199,15 +7189,15 @@
         <v>73</v>
       </c>
       <c r="I243" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>10</v>
       </c>
       <c r="B244" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D244" t="s">
         <v>106</v>
@@ -7225,18 +7215,18 @@
         <v>193</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>10</v>
       </c>
       <c r="B245" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D245" t="s">
         <v>106</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F245" t="s">
         <v>26</v>
@@ -7245,15 +7235,15 @@
         <v>26</v>
       </c>
       <c r="I245" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>10</v>
       </c>
       <c r="B246" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D246" t="s">
         <v>106</v>
@@ -7271,12 +7261,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>10</v>
       </c>
       <c r="B247" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D247" t="s">
         <v>106</v>
@@ -7294,12 +7284,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>10</v>
       </c>
       <c r="B248" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C248" t="b">
         <v>1</v>
@@ -7314,21 +7304,15 @@
         <v>36</v>
       </c>
       <c r="G248" t="s">
-        <v>203</v>
-      </c>
-      <c r="H248" t="s">
-        <v>177</v>
-      </c>
-      <c r="I248" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>10</v>
       </c>
       <c r="B249" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D249" t="s">
         <v>106</v>
@@ -7343,12 +7327,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>10</v>
       </c>
       <c r="B250" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D250" t="s">
         <v>106</v>
@@ -7363,12 +7347,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>10</v>
       </c>
       <c r="B251" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D251" t="s">
         <v>106</v>
@@ -7383,12 +7367,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>10</v>
       </c>
       <c r="B252" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D252" t="s">
         <v>106</v>
@@ -7403,12 +7387,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>10</v>
       </c>
       <c r="B253" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D253" t="s">
         <v>106</v>
@@ -7423,12 +7407,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>10</v>
       </c>
       <c r="B254" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D254" t="s">
         <v>106</v>
@@ -7443,12 +7427,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>10</v>
       </c>
       <c r="B255" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D255" t="s">
         <v>106</v>
@@ -7463,18 +7447,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>10</v>
       </c>
       <c r="B256" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D256" t="s">
         <v>106</v>
       </c>
       <c r="E256" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F256" t="s">
         <v>26</v>
@@ -7486,12 +7470,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>10</v>
       </c>
       <c r="B257" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D257" t="s">
         <v>106</v>
@@ -7506,12 +7490,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>10</v>
       </c>
       <c r="B258" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D258" t="s">
         <v>106</v>
@@ -7529,15 +7513,15 @@
         <v>73</v>
       </c>
       <c r="I258" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>10</v>
+      </c>
+      <c r="B259" t="s">
         <v>204</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A259" t="s">
-        <v>10</v>
-      </c>
-      <c r="B259" t="s">
-        <v>205</v>
       </c>
       <c r="D259" t="s">
         <v>106</v>
@@ -7555,18 +7539,18 @@
         <v>193</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>10</v>
       </c>
       <c r="B260" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D260" t="s">
         <v>106</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F260" t="s">
         <v>26</v>
@@ -7578,12 +7562,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>10</v>
       </c>
       <c r="B261" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D261" t="s">
         <v>106</v>
@@ -7601,12 +7585,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>10</v>
       </c>
       <c r="B262" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D262" t="s">
         <v>106</v>
@@ -7624,12 +7608,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>10</v>
       </c>
       <c r="B263" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C263" t="b">
         <v>1</v>
@@ -7644,21 +7628,15 @@
         <v>36</v>
       </c>
       <c r="G263" t="s">
-        <v>206</v>
-      </c>
-      <c r="H263" t="s">
-        <v>177</v>
-      </c>
-      <c r="I263" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>10</v>
       </c>
       <c r="B264" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D264" t="s">
         <v>106</v>
@@ -7673,12 +7651,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>10</v>
       </c>
       <c r="B265" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D265" t="s">
         <v>106</v>
@@ -7693,12 +7671,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>10</v>
       </c>
       <c r="B266" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D266" t="s">
         <v>106</v>
@@ -7713,12 +7691,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>10</v>
       </c>
       <c r="B267" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D267" t="s">
         <v>106</v>
@@ -7733,12 +7711,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>10</v>
       </c>
       <c r="B268" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D268" t="s">
         <v>106</v>
@@ -7753,12 +7731,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>10</v>
       </c>
       <c r="B269" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D269" t="s">
         <v>106</v>
@@ -7773,12 +7751,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>10</v>
       </c>
       <c r="B270" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D270" t="s">
         <v>106</v>
@@ -7793,18 +7771,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>10</v>
       </c>
       <c r="B271" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D271" t="s">
         <v>106</v>
       </c>
       <c r="E271" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F271" t="s">
         <v>26</v>
@@ -7816,12 +7794,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>10</v>
       </c>
       <c r="B272" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D272" t="s">
         <v>106</v>
@@ -7836,12 +7814,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>10</v>
       </c>
       <c r="B273" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D273" t="s">
         <v>106</v>
@@ -7859,15 +7837,15 @@
         <v>73</v>
       </c>
       <c r="I273" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>10</v>
       </c>
       <c r="B274" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D274" t="s">
         <v>106</v>
@@ -7885,18 +7863,18 @@
         <v>193</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>10</v>
       </c>
       <c r="B275" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D275" t="s">
         <v>106</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F275" t="s">
         <v>26</v>
@@ -7905,15 +7883,15 @@
         <v>26</v>
       </c>
       <c r="I275" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>10</v>
       </c>
       <c r="B276" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D276" t="s">
         <v>106</v>
@@ -7931,12 +7909,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>10</v>
       </c>
       <c r="B277" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D277" t="s">
         <v>106</v>
@@ -7954,12 +7932,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>10</v>
       </c>
       <c r="B278" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C278" t="b">
         <v>1</v>
@@ -7974,21 +7952,15 @@
         <v>36</v>
       </c>
       <c r="G278" t="s">
-        <v>210</v>
-      </c>
-      <c r="H278" t="s">
-        <v>177</v>
-      </c>
-      <c r="I278" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>10</v>
       </c>
       <c r="B279" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D279" t="s">
         <v>106</v>
@@ -8003,12 +7975,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>10</v>
       </c>
       <c r="B280" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D280" t="s">
         <v>106</v>
@@ -8023,12 +7995,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>10</v>
       </c>
       <c r="B281" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D281" t="s">
         <v>106</v>
@@ -8043,12 +8015,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>10</v>
       </c>
       <c r="B282" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D282" t="s">
         <v>106</v>
@@ -8063,12 +8035,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>10</v>
       </c>
       <c r="B283" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D283" t="s">
         <v>106</v>
@@ -8083,12 +8055,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>10</v>
       </c>
       <c r="B284" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D284" t="s">
         <v>106</v>
@@ -8103,12 +8075,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>10</v>
       </c>
       <c r="B285" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D285" t="s">
         <v>106</v>
@@ -8123,18 +8095,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>10</v>
       </c>
       <c r="B286" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D286" t="s">
         <v>106</v>
       </c>
       <c r="E286" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F286" t="s">
         <v>26</v>
@@ -8146,12 +8118,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>10</v>
       </c>
       <c r="B287" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D287" t="s">
         <v>106</v>
@@ -8166,12 +8138,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>10</v>
       </c>
       <c r="B288" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D288" t="s">
         <v>106</v>
@@ -8180,20 +8152,20 @@
         <v>94</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>10</v>
       </c>
       <c r="B289" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D289" t="s">
         <v>106</v>
@@ -8211,32 +8183,32 @@
         <v>193</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>10</v>
       </c>
       <c r="B290" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D290" t="s">
         <v>106</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F290" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G290" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>10</v>
       </c>
       <c r="B291" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D291" t="s">
         <v>106</v>
@@ -8254,12 +8226,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>10</v>
       </c>
       <c r="B292" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D292" t="s">
         <v>106</v>
@@ -8277,12 +8249,12 @@
         <v>-999</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>10</v>
       </c>
       <c r="B293" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C293" t="b">
         <v>1</v>
@@ -8297,21 +8269,15 @@
         <v>13</v>
       </c>
       <c r="G293" t="s">
-        <v>213</v>
-      </c>
-      <c r="H293" t="s">
-        <v>177</v>
-      </c>
-      <c r="I293" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>10</v>
       </c>
       <c r="B294" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D294" t="s">
         <v>106</v>
@@ -8326,12 +8292,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>10</v>
       </c>
       <c r="B295" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D295" t="s">
         <v>106</v>
@@ -8346,12 +8312,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>10</v>
       </c>
       <c r="B296" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D296" t="s">
         <v>106</v>
@@ -8366,12 +8332,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>10</v>
       </c>
       <c r="B297" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D297" t="s">
         <v>106</v>
@@ -8386,12 +8352,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>10</v>
       </c>
       <c r="B298" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D298" t="s">
         <v>106</v>
@@ -8406,12 +8372,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>10</v>
       </c>
       <c r="B299" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D299" t="s">
         <v>106</v>
@@ -8426,12 +8392,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>10</v>
       </c>
       <c r="B300" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D300" t="s">
         <v>106</v>
@@ -8447,13 +8413,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K300" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="treatment_surgery"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K300" xr:uid="{35411F09-EBB8-0141-861C-E6F1B855767B}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/docs/mci_cog_igm_rules_dcc.xlsx
+++ b/docs/mci_cog_igm_rules_dcc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bullenca/Work/Repos/ChildhoodCancerDataInitiative-Prefect_Pipeline/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA4E67F-788D-A542-9D06-943559000E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC71A2C-0CF6-BC43-8A8F-365880FB89B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="1600" windowWidth="30240" windowHeight="18980" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
+    <workbookView xWindow="4080" yWindow="1420" windowWidth="30240" windowHeight="18980" xr2:uid="{9DC53540-95BC-6744-B593-4545FF261AF8}"/>
   </bookViews>
   <sheets>
     <sheet name="cog_rules" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="222">
   <si>
     <t>source</t>
   </si>
@@ -6706,6 +6706,9 @@
       <c r="G221" t="s">
         <v>220</v>
       </c>
+      <c r="J221" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
